--- a/data/trans_dic/IP12_R1_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP12_R1_2023-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que limitaron su actividad por dolor 2023</t>
+          <t>Menores que limitaron su actividad por dolor 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,44; 8,03</t>
+          <t>1,46; 8,14</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,99</t>
+          <t>0,3; 3,33</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,04; 4,34</t>
+          <t>1,12; 4,63</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,85; 4,28</t>
+          <t>0,85; 3,97</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,54; 3,72</t>
+          <t>0,45; 3,66</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,01; 3,25</t>
+          <t>0,92; 3,25</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,28; 6,18</t>
+          <t>1,34; 6,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,79; 5,16</t>
+          <t>0,72; 5,09</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,51; 4,63</t>
+          <t>1,48; 4,56</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,17</t>
+          <t>0,0; 2,16</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,72; 4,74</t>
+          <t>0,64; 5,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,71</t>
+          <t>0,53; 2,78</t>
         </is>
       </c>
     </row>
@@ -771,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,39; 3,34</t>
+          <t>1,39; 3,33</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,11; 2,82</t>
+          <t>1,08; 2,83</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,42; 2,67</t>
+          <t>1,42; 2,69</t>
         </is>
       </c>
     </row>
@@ -803,4 +804,454 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que limitaron su actividad por dolor 2023 (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>4295</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1476</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>5771</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>1713; 9552</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>424; 4674</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2888; 11943</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>3759</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>4113</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>7872</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>1617; 7556</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>1146; 9341</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>4083; 14476</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>5944</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>4080</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>10024</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>2548; 12183</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1340; 9424</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>5559; 17105</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>723</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3900</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>4623</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3634</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>1160; 9220</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>1855; 9721</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>14721</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>13568</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>28290</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>9220; 22171</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>8264; 21555</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>20251; 38405</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP12_R1_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP12_R1_2023-Habitat-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que limitaron su actividad por dolor 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores que en las últimas 2 semanas limitaron su actividad por dolor (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,46; 8,14</t>
+          <t>1,54; 7,75</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,3; 3,33</t>
+          <t>0,31; 2,94</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,12; 4,63</t>
+          <t>1,19; 4,55</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,85; 3,97</t>
+          <t>0,82; 4,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,45; 3,66</t>
+          <t>0,44; 3,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,92; 3,25</t>
+          <t>0,96; 3,18</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,34; 6,43</t>
+          <t>1,46; 6,16</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,72; 5,09</t>
+          <t>0,84; 5,74</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,48; 4,56</t>
+          <t>1,47; 4,71</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,16</t>
+          <t>0,0; 1,99</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,64; 5,09</t>
+          <t>0,74; 5,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,53; 2,78</t>
+          <t>0,54; 3,0</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,39; 3,33</t>
+          <t>1,43; 3,28</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,08; 2,83</t>
+          <t>1,03; 2,85</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,42; 2,69</t>
+          <t>1,42; 2,68</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que limitaron su actividad por dolor 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores que en las últimas 2 semanas limitaron su actividad por dolor (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1713; 9552</t>
+          <t>1810; 9085</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>424; 4674</t>
+          <t>439; 4127</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2888; 11943</t>
+          <t>3077; 11722</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1617; 7556</t>
+          <t>1556; 7780</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1146; 9341</t>
+          <t>1124; 9130</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4083; 14476</t>
+          <t>4264; 14177</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2548; 12183</t>
+          <t>2761; 11679</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1340; 9424</t>
+          <t>1552; 10635</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5559; 17105</t>
+          <t>5502; 17651</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3634</t>
+          <t>0; 3345</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1160; 9220</t>
+          <t>1342; 9209</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1855; 9721</t>
+          <t>1874; 10467</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>9220; 22171</t>
+          <t>9523; 21824</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>8264; 21555</t>
+          <t>7886; 21745</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>20251; 38405</t>
+          <t>20271; 38237</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP12_R1_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP12_R1_2023-Habitat-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,54; 7,75</t>
+          <t>0,28; 3,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,94</t>
+          <t>1,39; 8,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,19; 4,55</t>
+          <t>1,1; 4,7</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,82; 4,08</t>
+          <t>0,5; 3,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,44; 3,58</t>
+          <t>0,85; 4,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,96; 3,18</t>
+          <t>1,01; 3,45</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>3,05%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,46; 6,16</t>
+          <t>0,83; 5,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,84; 5,74</t>
+          <t>1,77; 7,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,47; 4,71</t>
+          <t>1,71; 5,15</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,33%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,99</t>
+          <t>0,78; 4,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,74; 5,08</t>
+          <t>0,0; 2,1</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,54; 3,0</t>
+          <t>0,47; 2,75</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,43; 3,28</t>
+          <t>1,14; 2,95</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,03; 2,85</t>
+          <t>1,5; 3,56</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,42; 2,68</t>
+          <t>1,49; 2,84</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4295</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>4378</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5771</t>
+          <t>5826</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1810; 9085</t>
+          <t>354; 4153</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>439; 4127</t>
+          <t>1680; 9703</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3077; 11722</t>
+          <t>2707; 11616</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>3759</t>
+          <t>3953</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4113</t>
+          <t>3617</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7872</t>
+          <t>7571</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1556; 7780</t>
+          <t>1187; 9145</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1124; 9130</t>
+          <t>1562; 8183</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4264; 14177</t>
+          <t>4275; 14526</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5944</t>
+          <t>3930</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4080</t>
+          <t>5968</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10024</t>
+          <t>9898</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2761; 11679</t>
+          <t>1403; 8971</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1552; 10635</t>
+          <t>2763; 11470</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5502; 17651</t>
+          <t>5534; 16710</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>723</t>
+          <t>3794</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3900</t>
+          <t>696</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4623</t>
+          <t>4490</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3345</t>
+          <t>1321; 8400</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1342; 9209</t>
+          <t>0; 3516</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1874; 10467</t>
+          <t>1582; 9271</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>23</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>14721</t>
+          <t>13127</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>13568</t>
+          <t>14659</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>28290</t>
+          <t>27785</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>9523; 21824</t>
+          <t>7972; 20665</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>7886; 21745</t>
+          <t>9434; 22381</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>20271; 38237</t>
+          <t>19773; 37784</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP12_R1_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP12_R1_2023-Habitat-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,341 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que en las últimas 2 semanas limitaron su actividad por dolor (tasa de respuesta: 100,0%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>&lt;10.000 hab</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>1,15%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>3,62%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2,36%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>0,28; 3,3</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>1,39; 8,01</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>1,1; 4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>10-50.000 hab</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>1,67%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>1,96%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1,8%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>0,5; 3,86</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>0,85; 4,44</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1,01; 3,45</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>2,33%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>3,82%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>3,05%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>0,83; 5,33</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>1,77; 7,34</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>1,71; 5,15</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Capitales</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>2,24%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1,33%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>0,78; 4,96</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,1</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0,47; 2,75</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>1,87%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>2,33%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>2,09%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>1,14; 2,95</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>1,5; 3,56</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1,49; 2,84</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -879,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.01150518694857363</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.03615675564255454</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.0235896941753839</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>1449</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>4378</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>5826</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.002812746513769344</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.0138770980868166</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.01095927003915253</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>354; 4153</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>1680; 9703</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2707; 11616</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.03298561993466836</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.08014491236758138</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.04703366521773746</v>
       </c>
     </row>
     <row r="7">
@@ -952,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.0166664677974316</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.01961498304630884</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.01795612420282427</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>3953</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>3617</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>7571</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.005002614295856001</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.008467764068335977</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.0101384934788017</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>1187; 9145</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>1562; 8183</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>4275; 14526</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.03855494942040686</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.04437096158999598</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.03445285590994081</v>
       </c>
     </row>
     <row r="10">
@@ -1025,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.02334711576917477</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.03820498131008879</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.0304982331802291</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>3930</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>5968</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>9898</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.008334077603063867</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.01768875886885127</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.01705226888825428</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>1403; 8971</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>2763; 11470</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>5534; 16710</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.05329235163596347</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.07343255755764073</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.05148703625955148</v>
       </c>
     </row>
     <row r="13">
@@ -1098,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.02240148666477647</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.004164567959530563</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.01334349674591537</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>3794</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>696</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>4490</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.007799876002112902</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.004702506592229538</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>1321; 8400</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>0; 3516</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>1582; 9271</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.04959161477647869</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.02103325538975288</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.02754887546216815</v>
       </c>
     </row>
     <row r="16">
@@ -1171,69 +772,51 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.01872997507157947</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.02331090184581332</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.02089641777762587</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>13127</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>14659</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>27785</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.01137457475397697</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.01500279473365131</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.01487034949691942</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>7972; 20665</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>9434; 22381</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>19773; 37784</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.02948654580432733</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.03559112718174554</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.02841607912489146</v>
       </c>
     </row>
     <row r="19">
@@ -1254,4 +837,449 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que en las últimas 2 semanas limitaron su actividad por dolor (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>1449</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>4378</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>5826</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>354</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>1680</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>2707</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>4153</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>9703</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>11616</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>3953</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>3617</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>7571</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>1187</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>1562</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>4275</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>9145</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>8183</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>14526</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>3930</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>5968</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>9898</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>1403</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>2763</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>5534</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>8971</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>11470</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>16710</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>3794</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>696</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>4490</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>1321</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>1582</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>8400</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>3516</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>9271</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>13127</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>14659</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>27785</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>7972</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>9434</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>19773</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>20665</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>22381</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>37784</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>